--- a/artfynd/A 29232-2023 artfynd.xlsx
+++ b/artfynd/A 29232-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29232-2023 artfynd.xlsx
+++ b/artfynd/A 29232-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111210888</v>
+        <v>111596832</v>
       </c>
       <c r="B2" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1106</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björkmossen 180 m NW, Upl</t>
+          <t>Björkmossen 139 m NE, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654464.3914330448</v>
+        <v>654305</v>
       </c>
       <c r="R2" t="n">
-        <v>6690770.276086448</v>
+        <v>6690856</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111210836</v>
+        <v>111596833</v>
       </c>
       <c r="B3" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,49 +796,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1106</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björkmossen 421 m NW, Upl</t>
+          <t>Björkmossen 319 m N, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654331.8535550121</v>
+        <v>654190</v>
       </c>
       <c r="R3" t="n">
-        <v>6690978.885022949</v>
+        <v>6691090</v>
       </c>
       <c r="S3" t="n">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,22 +853,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,57 +895,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111210891</v>
+        <v>111596831</v>
       </c>
       <c r="B4" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkmossen 401 m NW, Upl</t>
+          <t>Björkmossen 304 m N, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654370.8847137196</v>
+        <v>654195</v>
       </c>
       <c r="R4" t="n">
-        <v>6690972.110634593</v>
+        <v>6691076</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,22 +963,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,57 +1005,55 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111210894</v>
+        <v>111210851</v>
       </c>
       <c r="B5" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkmossen 579 m NW, Upl</t>
+          <t>Björkmossen 168 m N, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654181.8024364103</v>
+        <v>654479</v>
       </c>
       <c r="R5" t="n">
-        <v>6691073.684188806</v>
+        <v>6690762</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,15 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111210898</v>
+        <v>111596825</v>
       </c>
       <c r="B6" t="n">
-        <v>99413</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,45 +1130,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björkmossen 182 m N, Upl</t>
+          <t>Björkmossen 246 m E, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654474.1403182282</v>
+        <v>654442</v>
       </c>
       <c r="R6" t="n">
-        <v>6690774.657352869</v>
+        <v>6690766</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1187,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1235,7 +1197,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1267,66 +1229,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111210759</v>
+        <v>111596836</v>
       </c>
       <c r="B7" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björkmossen 418 m NW, Upl</t>
+          <t>Björkmossen 206 m E, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654327.1052996945</v>
+        <v>654400</v>
       </c>
       <c r="R7" t="n">
-        <v>6690973.724659374</v>
+        <v>6690787</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1350,22 +1297,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,6 +1321,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1392,65 +1340,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111210902</v>
+        <v>111596838</v>
       </c>
       <c r="B8" t="n">
-        <v>99413</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björkmossen 581 m NW, Upl</t>
+          <t>Björkmossen 141 m NE, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654184.6094705934</v>
+        <v>654275</v>
       </c>
       <c r="R8" t="n">
-        <v>6691077.770187957</v>
+        <v>6690886</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1474,30 +1408,36 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Luktar just ingenting. Smakar gammalt papper typ. Tar en liten bit från två olika fruktkroppar men kan inte känna nån skarp smak. Färgar av sig på fingrarna. Utifrån miljön bör det ändå vara skarp dropptaggsvamp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1516,57 +1456,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111210889</v>
+        <v>111596844</v>
       </c>
       <c r="B9" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björkmossen 233 m NW, Upl</t>
+          <t>Björkmossen 284 m E, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654386.9171590789</v>
+        <v>654479</v>
       </c>
       <c r="R9" t="n">
-        <v>6690793.271922525</v>
+        <v>6690759</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,22 +1532,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rätt stark men angenäm doft av bittermandel.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,6 +1561,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1632,15 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111210899</v>
+        <v>111596830</v>
       </c>
       <c r="B10" t="n">
-        <v>99413</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,41 +1591,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björkmossen 197 m NW, Upl</t>
+          <t>Björkmossen 277 m N, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654442.0276892063</v>
+        <v>654228</v>
       </c>
       <c r="R10" t="n">
-        <v>6690782.220807365</v>
+        <v>6691046</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,22 +1648,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,57 +1690,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111210896</v>
+        <v>111596843</v>
       </c>
       <c r="B11" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>5448</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björkmossen 188 m NW, Upl</t>
+          <t>Björkmossen 282 m E, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654457.1343136837</v>
+        <v>654477</v>
       </c>
       <c r="R11" t="n">
-        <v>6690777.40688647</v>
+        <v>6690758</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1822,22 +1766,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Väldigt svag doft.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1864,65 +1813,51 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111210903</v>
+        <v>111596840</v>
       </c>
       <c r="B12" t="n">
-        <v>99413</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björkmossen 177 m N, Upl</t>
+          <t>Björkmossen 180 m NE, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654478.2542368192</v>
+        <v>654329</v>
       </c>
       <c r="R12" t="n">
-        <v>6690771.360534019</v>
+        <v>6690891</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1946,22 +1881,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fuktig mark med nästan bara gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1988,60 +1928,59 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111210851</v>
+        <v>111596842</v>
       </c>
       <c r="B13" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björkmossen 168 m N, Upl</t>
+          <t>Björkmossen 289 m NE, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654479.6242423328</v>
+        <v>654342</v>
       </c>
       <c r="R13" t="n">
-        <v>6690762.492034903</v>
+        <v>6691020</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2065,22 +2004,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Fuktig mark med mest gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,57 +2051,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111210890</v>
+        <v>111596822</v>
       </c>
       <c r="B14" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björkmossen 282 m NW, Upl</t>
+          <t>Björkmossen 300 m SE, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654381.6316504544</v>
+        <v>654488</v>
       </c>
       <c r="R14" t="n">
-        <v>6690847.598552646</v>
+        <v>6690707</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2181,22 +2119,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2223,15 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111210904</v>
+        <v>111210764</v>
       </c>
       <c r="B15" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,49 +2172,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björkmossen 185 m NW, Upl</t>
+          <t>Björkmossen 222 m NW, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654440.1367665792</v>
+        <v>654453</v>
       </c>
       <c r="R15" t="n">
-        <v>6690768.254672054</v>
+        <v>6690811</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2310,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2320,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2347,19 +2280,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111210764</v>
+        <v>111596815</v>
       </c>
       <c r="B16" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2395,17 +2323,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björkmossen 222 m NW, Upl</t>
+          <t>Björkmossen 262 m E, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654452.709289292</v>
+        <v>654455</v>
       </c>
       <c r="R16" t="n">
-        <v>6690811.437644606</v>
+        <v>6690804</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2429,22 +2357,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2471,15 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111210895</v>
+        <v>111210759</v>
       </c>
       <c r="B17" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,46 +2410,47 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björkmossen 624 m NW, Upl</t>
+          <t>Björkmossen 418 m NW, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654159.3005364275</v>
+        <v>654327</v>
       </c>
       <c r="R17" t="n">
-        <v>6691112.400855604</v>
+        <v>6690973</v>
       </c>
       <c r="S17" t="n">
         <v>6</v>
@@ -2558,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2568,7 +2492,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2595,15 +2519,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111210908</v>
+        <v>111596818</v>
       </c>
       <c r="B18" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2611,49 +2530,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>208245</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björkmossen 238 m NW, Upl</t>
+          <t>Björkmossen 269 m N, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654384.206877493</v>
+        <v>654176</v>
       </c>
       <c r="R18" t="n">
-        <v>6690798.612050951</v>
+        <v>6691040</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2677,22 +2593,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2719,64 +2635,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111596844</v>
+        <v>111210904</v>
       </c>
       <c r="B19" t="n">
-        <v>91623</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4368</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Björkmossen 284 m E, Upl</t>
+          <t>Björkmossen 185 m NW, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654479</v>
+        <v>654440</v>
       </c>
       <c r="R19" t="n">
-        <v>6690759</v>
+        <v>6690768</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2800,27 +2712,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rätt stark men angenäm doft av bittermandel.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2829,7 +2736,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2848,15 +2754,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111596840</v>
+        <v>111210908</v>
       </c>
       <c r="B20" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2864,40 +2765,49 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Björkmossen 180 m NE, Upl</t>
+          <t>Björkmossen 238 m NW, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654329.1032540089</v>
+        <v>654384</v>
       </c>
       <c r="R20" t="n">
-        <v>6690891.489788271</v>
+        <v>6690798</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2921,27 +2831,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Fuktig mark med nästan bara gran.</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2968,65 +2873,60 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111596815</v>
+        <v>111596895</v>
       </c>
       <c r="B21" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Björkmossen 262 m E, Upl</t>
+          <t>Björkmossen 238 m E, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654455.0078743013</v>
+        <v>654433</v>
       </c>
       <c r="R21" t="n">
-        <v>6690804.096419388</v>
+        <v>6690769</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3055,7 +2955,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3065,7 +2965,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Cirka.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3092,15 +2997,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111596853</v>
+        <v>111596897</v>
       </c>
       <c r="B22" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3108,41 +3008,49 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björkmossen 243 m NE, Upl</t>
+          <t>Björkmossen 227 m E, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654327.0633065681</v>
+        <v>654422</v>
       </c>
       <c r="R22" t="n">
-        <v>6690974.714669497</v>
+        <v>6690769</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3171,7 +3079,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3181,7 +3089,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, helt tjockt med plantor så går ej att räkna.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3208,56 +3121,60 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111596833</v>
+        <v>111596900</v>
       </c>
       <c r="B23" t="n">
-        <v>89601</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1106</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Björkmossen 319 m N, Upl</t>
+          <t>Björkmossen 230 m E, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654189.5598878536</v>
+        <v>654425</v>
       </c>
       <c r="R23" t="n">
-        <v>6691089.881082441</v>
+        <v>6690762</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3286,7 +3203,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3296,7 +3213,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Uppskattat antal.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3323,56 +3245,56 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111596825</v>
+        <v>111210898</v>
       </c>
       <c r="B24" t="n">
-        <v>89183</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3215</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björkmossen 246 m E, Upl</t>
+          <t>Björkmossen 182 m N, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654441.2125153403</v>
+        <v>654474</v>
       </c>
       <c r="R24" t="n">
-        <v>6690766.31663138</v>
+        <v>6690775</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3396,7 +3318,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3406,7 +3328,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3438,56 +3360,52 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111596832</v>
+        <v>111210899</v>
       </c>
       <c r="B25" t="n">
-        <v>89601</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1106</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Björkmossen 139 m NE, Upl</t>
+          <t>Björkmossen 197 m NW, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654305.2642562862</v>
+        <v>654443</v>
       </c>
       <c r="R25" t="n">
-        <v>6690856.260986242</v>
+        <v>6690782</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3511,22 +3429,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3553,54 +3471,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111596854</v>
+        <v>111210902</v>
       </c>
       <c r="B26" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Björkmossen 296 m NE, Upl</t>
+          <t>Björkmossen 581 m NW, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654358.4983336662</v>
+        <v>654185</v>
       </c>
       <c r="R26" t="n">
-        <v>6691018.199085277</v>
+        <v>6691078</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
@@ -3627,22 +3548,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3669,42 +3590,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111596897</v>
+        <v>111210903</v>
       </c>
       <c r="B27" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>221235</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3717,17 +3633,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Björkmossen 227 m E, Upl</t>
+          <t>Björkmossen 177 m N, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654422.181084068</v>
+        <v>654479</v>
       </c>
       <c r="R27" t="n">
-        <v>6690769.97221576</v>
+        <v>6690771</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3751,27 +3667,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Uppskattat antal, helt tjockt med plantor så går ej att räkna.</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3798,37 +3709,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111596852</v>
+        <v>111596856</v>
       </c>
       <c r="B28" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3838,17 +3744,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Björkmossen 202 m E, Upl</t>
+          <t>Björkmossen 329 m E, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654397.1701999516</v>
+        <v>654522</v>
       </c>
       <c r="R28" t="n">
-        <v>6690785.772233884</v>
+        <v>6690735</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3877,7 +3783,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3887,7 +3793,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3914,42 +3820,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111596851</v>
+        <v>111596859</v>
       </c>
       <c r="B29" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3962,17 +3863,17 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Björkmossen 266 m E, Upl</t>
+          <t>Björkmossen 311 m SE, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654461.5003862897</v>
+        <v>654503</v>
       </c>
       <c r="R29" t="n">
-        <v>6690768.169657714</v>
+        <v>6690725</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4001,7 +3902,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4011,7 +3912,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4038,53 +3939,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111596830</v>
+        <v>111596865</v>
       </c>
       <c r="B30" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>221235</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Björkmossen 277 m N, Upl</t>
+          <t>Björkmossen 270 m E, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654228.1590436924</v>
+        <v>654464</v>
       </c>
       <c r="R30" t="n">
-        <v>6691046.391933746</v>
+        <v>6690751</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -4116,7 +4021,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4126,7 +4031,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4153,42 +4058,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111596900</v>
+        <v>111596867</v>
       </c>
       <c r="B31" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>221235</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4201,17 +4101,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Björkmossen 230 m E, Upl</t>
+          <t>Björkmossen 254 m N, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654424.5006373823</v>
+        <v>654194</v>
       </c>
       <c r="R31" t="n">
-        <v>6690762.135856108</v>
+        <v>6691025</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4240,7 +4140,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4250,12 +4150,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Uppskattat antal.</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4282,15 +4177,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111596850</v>
+        <v>111210888</v>
       </c>
       <c r="B32" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4322,17 +4212,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Björkmossen 311 m SE, Upl</t>
+          <t>Björkmossen 180 m NW, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654503.0392390501</v>
+        <v>654464</v>
       </c>
       <c r="R32" t="n">
-        <v>6690725.795596425</v>
+        <v>6690771</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4356,22 +4246,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4398,15 +4288,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111596859</v>
+        <v>111210889</v>
       </c>
       <c r="B33" t="n">
-        <v>99413</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4414,49 +4299,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Björkmossen 311 m SE, Upl</t>
+          <t>Björkmossen 233 m NW, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654503.0812791266</v>
+        <v>654387</v>
       </c>
       <c r="R33" t="n">
-        <v>6690724.805518131</v>
+        <v>6690793</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4480,22 +4357,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4522,15 +4399,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111596895</v>
+        <v>111210890</v>
       </c>
       <c r="B34" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4538,49 +4410,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Björkmossen 238 m E, Upl</t>
+          <t>Björkmossen 282 m NW, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654433.1528313066</v>
+        <v>654381</v>
       </c>
       <c r="R34" t="n">
-        <v>6690768.95009726</v>
+        <v>6690847</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4604,27 +4468,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Cirka.</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4651,56 +4510,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111596831</v>
+        <v>111210891</v>
       </c>
       <c r="B35" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Björkmossen 304 m N, Upl</t>
+          <t>Björkmossen 401 m NW, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654194.6095515667</v>
+        <v>654371</v>
       </c>
       <c r="R35" t="n">
-        <v>6691076.210478476</v>
+        <v>6690973</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4724,22 +4579,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4766,15 +4621,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111596867</v>
+        <v>111210893</v>
       </c>
       <c r="B36" t="n">
-        <v>99413</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4782,26 +4632,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4814,17 +4664,17 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Björkmossen 254 m N, Upl</t>
+          <t>Björkmossen 506 m NW, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654194.2912932655</v>
+        <v>654226</v>
       </c>
       <c r="R36" t="n">
-        <v>6691025.120983994</v>
+        <v>6691016</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4848,22 +4698,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4890,15 +4740,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>111596842</v>
+        <v>111210894</v>
       </c>
       <c r="B37" t="n">
-        <v>91626</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4906,48 +4751,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Björkmossen 289 m NE, Upl</t>
+          <t>Björkmossen 579 m NW, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654342</v>
+        <v>654181</v>
       </c>
       <c r="R37" t="n">
-        <v>6691020</v>
+        <v>6691074</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4971,27 +4809,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Fuktig mark med mest gran.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5018,15 +4851,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111596856</v>
+        <v>111210895</v>
       </c>
       <c r="B38" t="n">
-        <v>99413</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5034,41 +4862,49 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Björkmossen 329 m E, Upl</t>
+          <t>Björkmossen 624 m NW, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654521.5244157268</v>
+        <v>654159</v>
       </c>
       <c r="R38" t="n">
-        <v>6690735.0113796</v>
+        <v>6691112</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5092,22 +4928,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5134,15 +4970,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111596818</v>
+        <v>111210896</v>
       </c>
       <c r="B39" t="n">
-        <v>57552</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5150,46 +4981,41 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>208245</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Björkmossen 269 m N, Upl</t>
+          <t>Björkmossen 188 m NW, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654176.2874868776</v>
+        <v>654457</v>
       </c>
       <c r="R39" t="n">
-        <v>6691039.730467042</v>
+        <v>6690777</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5213,22 +5039,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5255,64 +5081,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111596843</v>
+        <v>111596850</v>
       </c>
       <c r="B40" t="n">
-        <v>90709</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5448</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Björkmossen 282 m E, Upl</t>
+          <t>Björkmossen 311 m SE, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654476.3214109741</v>
+        <v>654503</v>
       </c>
       <c r="R40" t="n">
-        <v>6690758.38440035</v>
+        <v>6690726</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5341,7 +5155,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5351,12 +5165,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Väldigt svag doft.</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5383,15 +5192,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>111596836</v>
+        <v>111596851</v>
       </c>
       <c r="B41" t="n">
-        <v>90678</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5399,40 +5203,49 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Björkmossen 206 m E, Upl</t>
+          <t>Björkmossen 266 m E, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654400.0822726104</v>
+        <v>654461</v>
       </c>
       <c r="R41" t="n">
-        <v>6690787.383569676</v>
+        <v>6690769</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5461,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5471,7 +5284,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5480,7 +5293,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5496,6 +5308,450 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>111596852</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Björkmossen 202 m E, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>654397</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6690785</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>111596853</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Björkmossen 243 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>654327</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6690975</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>111596854</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Björkmossen 296 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>654358</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6691018</v>
+      </c>
+      <c r="S44" t="n">
+        <v>8</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>111596855</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Björkmossen 242 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>654233</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6691011</v>
+      </c>
+      <c r="S45" t="n">
+        <v>11</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29232-2023 artfynd.xlsx
+++ b/artfynd/A 29232-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596832</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596833</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596831</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210851</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596825</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596836</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1453,6 +1488,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596838</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1577,6 +1617,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596844</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1687,6 +1732,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596830</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1810,6 +1860,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596843</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1925,6 +1980,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596840</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2048,6 +2108,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596842</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2158,6 +2223,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596822</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2277,6 +2347,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210764</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2396,6 +2471,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596815</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2516,6 +2596,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210759</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2632,6 +2717,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596818</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2751,6 +2841,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210904</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2870,6 +2965,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210908</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2994,6 +3094,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596895</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3118,6 +3223,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596897</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3242,6 +3352,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596900</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3357,6 +3472,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210898</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3468,6 +3588,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210899</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3587,6 +3712,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210902</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3706,6 +3836,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210903</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3817,6 +3952,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596856</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3936,6 +4076,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596859</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4055,6 +4200,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596865</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4174,6 +4324,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596867</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4285,6 +4440,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210888</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4396,6 +4556,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210889</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4507,6 +4672,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210890</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4618,6 +4788,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210891</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4737,6 +4912,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210893</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4848,6 +5028,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210894</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4967,6 +5152,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210895</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5078,6 +5268,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210896</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5189,6 +5384,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596850</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5308,6 +5508,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596851</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5419,6 +5624,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596852</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5530,6 +5740,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596853</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5641,6 +5856,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596854</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5752,8 +5972,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596855</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>